--- a/data/trans_bre/P8_1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P8_1_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,78</t>
+          <t>6,83; 14,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 16,75</t>
+          <t>7,43; 15,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,84</t>
+          <t>6,62; 15,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 8,87</t>
+          <t>-0,44; 8,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,03; 152,28</t>
+          <t>54,51; 156,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,86; 126,31</t>
+          <t>41,6; 117,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,14; 118,05</t>
+          <t>37,53; 114,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 63,37</t>
+          <t>-1,63; 58,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,49</t>
+          <t>6,67; 13,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 12,07</t>
+          <t>4,87; 12,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,58</t>
+          <t>5,01; 12,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 11,42</t>
+          <t>-40,07; 11,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,05; 137,61</t>
+          <t>51,21; 136,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,4; 86,8</t>
+          <t>27,45; 88,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,23; 94,14</t>
+          <t>31,31; 92,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 106,83</t>
+          <t>-65,61; 103,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 16,32</t>
+          <t>8,14; 16,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 15,83</t>
+          <t>7,59; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,56</t>
+          <t>4,24; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 4,35</t>
+          <t>-11,97; 4,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,51; 156,98</t>
+          <t>55,26; 156,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,42; 156,4</t>
+          <t>54,24; 151,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,09; 101,84</t>
+          <t>29,04; 105,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 25,78</t>
+          <t>-59,36; 25,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,81</t>
+          <t>6,26; 12,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,57</t>
+          <t>7,86; 14,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,27</t>
+          <t>4,21; 11,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 11,01</t>
+          <t>2,92; 11,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,97; 134,32</t>
+          <t>53,82; 135,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,4; 111,69</t>
+          <t>48,13; 111,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,83; 104,82</t>
+          <t>29,2; 103,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 84,98</t>
+          <t>17,96; 85,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,04</t>
+          <t>8,41; 12,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,67</t>
+          <t>8,66; 12,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,62</t>
+          <t>7,08; 10,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 6,37</t>
+          <t>-17,8; 6,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,36; 115,43</t>
+          <t>70,26; 115,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,04; 92,82</t>
+          <t>55,61; 92,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,66; 81,36</t>
+          <t>48,08; 82,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 43,65</t>
+          <t>-46,88; 46,51</t>
         </is>
       </c>
     </row>
